--- a/data/trans_dic/IP42B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>La persona sustentadora principal recibe una pensión</t>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 49,61</t>
+          <t>18,04; 50,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,54; 58,8</t>
+          <t>26,96; 59,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 23,67</t>
+          <t>4,42; 24,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 39,77</t>
+          <t>7,79; 39,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,09; 39,14</t>
+          <t>14,95; 39,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 23,75</t>
+          <t>4,55; 23,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 39,62</t>
+          <t>16,63; 39,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,7; 43,32</t>
+          <t>24,3; 42,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 20,46</t>
+          <t>5,87; 20,46</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,07</t>
+          <t>1,39; 8,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 17,14</t>
+          <t>7,23; 16,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,94</t>
+          <t>4,77; 12,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,63</t>
+          <t>2,46; 9,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 18,22</t>
+          <t>8,41; 18,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 10,2</t>
+          <t>3,98; 10,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,49</t>
+          <t>2,63; 7,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,1</t>
+          <t>9,08; 15,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 9,92</t>
+          <t>5,11; 9,69</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 28,8</t>
+          <t>3,36; 27,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 23,71</t>
+          <t>2,88; 25,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 18,69</t>
+          <t>2,32; 19,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,37</t>
+          <t>0,0; 18,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,03</t>
+          <t>0,0; 18,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 17,25</t>
+          <t>2,06; 17,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 16,71</t>
+          <t>2,74; 16,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 16,52</t>
+          <t>3,14; 16,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 14,14</t>
+          <t>4,04; 15,93</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,94</t>
+          <t>5,59; 13,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,54; 20,23</t>
+          <t>11,22; 20,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,02</t>
+          <t>5,65; 12,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,93</t>
+          <t>4,31; 11,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 18,63</t>
+          <t>10,14; 18,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,64</t>
+          <t>5,11; 10,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,77</t>
+          <t>5,68; 10,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,86</t>
+          <t>12,05; 18,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,07</t>
+          <t>6,03; 10,32</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6936</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10909</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8169</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11141</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>19079</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6855</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3909; 10970</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6986; 15344</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1247; 7005</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1516; 7725</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4779; 12603</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1322; 6719</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6840; 16192</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>14065; 24838</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3359; 11714</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3449</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14942</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11030</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6193</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16717</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9641</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>31659</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>22468</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1332; 7709</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9446; 21701</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6732; 17443</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2807; 11052</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10902; 23594</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6781; 17562</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5527; 15890</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>23623; 40919</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>15932; 30182</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2373</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3478</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3880</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5273</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>624; 5143</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>639; 5644</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>761; 6244</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4748</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>722; 6276</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1248; 7394</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1524; 8090</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2743; 10802</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12496</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28224</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17029</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>54618</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>34596</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7602; 18744</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20048; 36695</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11426; 24573</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6922; 17956</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>19076; 35275</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11986; 24817</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>16854; 32322</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>44175; 66638</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>26344; 45078</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP42B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,04; 50,62</t>
+          <t>18,03; 51,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,96; 59,21</t>
+          <t>25,5; 57,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 24,82</t>
+          <t>4,26; 25,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,79; 39,68</t>
+          <t>7,74; 39,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 39,43</t>
+          <t>14,93; 38,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 23,14</t>
+          <t>4,5; 25,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,63; 39,36</t>
+          <t>16,86; 40,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,3; 42,91</t>
+          <t>24,27; 43,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 20,46</t>
+          <t>6,12; 20,98</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,05</t>
+          <t>1,38; 7,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 16,62</t>
+          <t>7,65; 17,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 12,37</t>
+          <t>5,05; 12,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,67</t>
+          <t>2,45; 9,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 18,19</t>
+          <t>8,54; 18,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,3</t>
+          <t>4,16; 10,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,56</t>
+          <t>2,57; 7,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 15,72</t>
+          <t>9,13; 15,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,69</t>
+          <t>5,05; 9,82</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 27,7</t>
+          <t>3,33; 29,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 25,41</t>
+          <t>3,05; 25,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 19,05</t>
+          <t>2,16; 18,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,22</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,0</t>
+          <t>0,0; 19,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 17,91</t>
+          <t>2,06; 17,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 16,2</t>
+          <t>2,79; 16,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 16,65</t>
+          <t>3,07; 16,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 15,93</t>
+          <t>3,78; 14,38</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 13,78</t>
+          <t>5,84; 13,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,22; 20,53</t>
+          <t>11,87; 20,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 12,16</t>
+          <t>6,03; 12,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,17</t>
+          <t>4,26; 10,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 18,76</t>
+          <t>10,34; 18,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,58</t>
+          <t>4,91; 10,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,89</t>
+          <t>5,84; 11,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 18,17</t>
+          <t>11,94; 18,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,32</t>
+          <t>6,01; 10,41</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3909; 10970</t>
+          <t>3907; 11074</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6986; 15344</t>
+          <t>6608; 14956</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1247; 7005</t>
+          <t>1202; 7071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1516; 7725</t>
+          <t>1507; 7723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4779; 12603</t>
+          <t>4774; 12377</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1322; 6719</t>
+          <t>1306; 7269</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6840; 16192</t>
+          <t>6936; 16482</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14065; 24838</t>
+          <t>14049; 25039</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3359; 11714</t>
+          <t>3501; 12009</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1332; 7709</t>
+          <t>1321; 7030</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9446; 21701</t>
+          <t>9994; 22945</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6732; 17443</t>
+          <t>7124; 16973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2807; 11052</t>
+          <t>2805; 10976</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10902; 23594</t>
+          <t>11077; 24262</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6781; 17562</t>
+          <t>7084; 18026</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5527; 15890</t>
+          <t>5392; 15508</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23623; 40919</t>
+          <t>23758; 41622</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15932; 30182</t>
+          <t>15729; 30589</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>624; 5143</t>
+          <t>618; 5439</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>639; 5644</t>
+          <t>678; 5635</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>761; 6244</t>
+          <t>708; 6061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4930</t>
+          <t>0; 4149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4748</t>
+          <t>0; 5083</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>722; 6276</t>
+          <t>721; 6273</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1248; 7394</t>
+          <t>1271; 7577</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1524; 8090</t>
+          <t>1492; 8071</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2743; 10802</t>
+          <t>2562; 9751</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7602; 18744</t>
+          <t>7944; 18363</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20048; 36695</t>
+          <t>21221; 37511</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11426; 24573</t>
+          <t>12180; 24540</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6922; 17956</t>
+          <t>6845; 17396</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19076; 35275</t>
+          <t>19449; 35299</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11986; 24817</t>
+          <t>11510; 25294</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16854; 32322</t>
+          <t>17329; 33111</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44175; 66638</t>
+          <t>43786; 66645</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26344; 45078</t>
+          <t>26230; 45458</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP42B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25,56%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>32,01%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>42,1%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,11%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,03; 51,1</t>
+          <t>10,17; 39,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,5; 57,71</t>
+          <t>15,09; 39,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 25,06</t>
+          <t>4,54; 23,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 39,67</t>
+          <t>17,89; 49,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,93; 38,72</t>
+          <t>26,54; 58,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 25,04</t>
+          <t>4,19; 23,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,86; 40,06</t>
+          <t>16,37; 39,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,27; 43,26</t>
+          <t>23,7; 43,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 20,98</t>
+          <t>6,03; 20,46</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>11,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,34</t>
+          <t>2,42; 9,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 17,57</t>
+          <t>8,54; 18,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 12,03</t>
+          <t>3,75; 10,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,61</t>
+          <t>1,41; 8,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 18,71</t>
+          <t>7,51; 17,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 10,57</t>
+          <t>4,81; 11,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,38</t>
+          <t>2,66; 7,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 15,99</t>
+          <t>9,13; 16,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,82</t>
+          <t>4,93; 9,92</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,37%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>10,68%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 29,29</t>
+          <t>0,0; 19,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 25,37</t>
+          <t>0,0; 16,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 18,49</t>
+          <t>2,07; 17,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>3,33; 28,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,28</t>
+          <t>2,81; 23,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 17,9</t>
+          <t>2,23; 18,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 16,6</t>
+          <t>2,81; 16,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 16,61</t>
+          <t>3,6; 16,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,38</t>
+          <t>3,55; 14,14</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>9,19%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>15,79%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,5</t>
+          <t>4,37; 10,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 20,99</t>
+          <t>10,09; 18,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,14</t>
+          <t>4,81; 10,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,82</t>
+          <t>5,52; 13,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,77</t>
+          <t>11,54; 20,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 10,78</t>
+          <t>5,69; 12,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,15</t>
+          <t>5,83; 10,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,94; 18,17</t>
+          <t>11,98; 17,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,41</t>
+          <t>5,96; 10,07</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8169</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>6936</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>10909</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3416</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4204</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8169</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3439</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3907; 11074</t>
+          <t>1980; 7742</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6608; 14956</t>
+          <t>4823; 12512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1202; 7071</t>
+          <t>1317; 6895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1507; 7723</t>
+          <t>3878; 10752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4774; 12377</t>
+          <t>6878; 15236</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1306; 7269</t>
+          <t>1184; 6679</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6936; 16482</t>
+          <t>6736; 16298</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14049; 25039</t>
+          <t>13719; 25071</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3501; 12009</t>
+          <t>3454; 11711</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6193</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16717</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3449</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>14942</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11030</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6193</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16717</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11438</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1321; 7030</t>
+          <t>2764; 11000</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9994; 22945</t>
+          <t>11079; 23631</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7124; 16973</t>
+          <t>6396; 17395</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2805; 10976</t>
+          <t>1347; 7728</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11077; 24262</t>
+          <t>9802; 22387</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7084; 18026</t>
+          <t>6788; 16840</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5392; 15508</t>
+          <t>5595; 15733</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23758; 41622</t>
+          <t>23764; 41913</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15729; 30589</t>
+          <t>15372; 30919</t>
         </is>
       </c>
     </row>
@@ -1526,27 +1526,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2111</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2373</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2584</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2690</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>618; 5439</t>
+          <t>0; 5243</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>678; 5635</t>
+          <t>0; 4228</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>708; 6061</t>
+          <t>724; 6042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4149</t>
+          <t>618; 5348</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5083</t>
+          <t>623; 5265</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>721; 6273</t>
+          <t>731; 6127</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1271; 7577</t>
+          <t>1280; 7627</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1492; 8071</t>
+          <t>1747; 8027</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2562; 9751</t>
+          <t>2409; 9593</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>12496</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>28224</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17029</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17567</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7944; 18363</t>
+          <t>7026; 17578</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21221; 37511</t>
+          <t>18970; 35036</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12180; 24540</t>
+          <t>11284; 24965</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6845; 17396</t>
+          <t>7509; 18963</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19449; 35299</t>
+          <t>20630; 36151</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11510; 25294</t>
+          <t>11500; 24287</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17329; 33111</t>
+          <t>17297; 31965</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43786; 66645</t>
+          <t>43936; 65513</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26230; 45458</t>
+          <t>26016; 43951</t>
         </is>
       </c>
     </row>
